--- a/tm/04_hesap_tablolari.xlsx
+++ b/tm/04_hesap_tablolari.xlsx
@@ -3388,7 +3388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
         <v>47</v>
       </c>
@@ -3436,7 +3436,7 @@
         <v>1.93236714975845</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
         <v>49</v>
       </c>
@@ -6045,7 +6045,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
         <v>168</v>
       </c>
@@ -6205,7 +6205,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
         <v>170</v>
       </c>
